--- a/assets/constructions/examples/ctd_tsmb_thread.xlsx
+++ b/assets/constructions/examples/ctd_tsmb_thread.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:BD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -684,103 +684,138 @@
           <t>thr_id</t>
         </is>
       </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R006.0612-22/CN45F</t>
+          <t>MS429TH28UNL16LVBX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DUEMMEL</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ULTRAMINI</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>Microscope</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>VAR_MS4</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>VARGUS</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PMKS</t>
+          <t>PMKNSH</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>2.3</v>
+        <v>0.92</v>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
-        <v>5.3</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>22</v>
-      </c>
-      <c r="P2" t="n">
-        <v>36.35</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>37</v>
+        <v>35.4</v>
       </c>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="S2" t="n">
+        <v>60</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
         <v>0.65</v>
       </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.25</v>
-      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>F</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6H</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+          <t>2A/2B</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.52</v>
+      </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>M60</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr"/>
+          <t>UN60</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>18.4</v>
+      </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>VARGUS_D:6</t>
+          <t>VARGUS_D:4</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -790,12 +825,12 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>CN45F</t>
+          <t>VBX</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>TIN</t>
+          <t>TiCN</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr"/>
@@ -817,15 +852,34 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ultramini,pdf</t>
+          <t>2019 / Groovex Catalog</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>3202.05</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L005.0510-15/AL41F</t>
+          <t>R005.0205-15/AL41F</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -865,7 +919,7 @@
         <v>15</v>
       </c>
       <c r="P3" t="n">
-        <v>29.45</v>
+        <v>29.65</v>
       </c>
       <c r="Q3" t="n">
         <v>30</v>
@@ -873,17 +927,17 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>0.55</v>
+        <v>0.27</v>
       </c>
       <c r="U3" t="n">
-        <v>0.55</v>
+        <v>0.35</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -909,7 +963,7 @@
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr"/>
@@ -958,25 +1012,52 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>51.68</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>4751.13</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BTH1.00ISO.054916.RETC</t>
+          <t>M439TH0.50ISOL16RVBX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BRICE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>VARGUS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Microscope</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VAR_M5</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>VAR_M4</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>VARGUS</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>PMKNSH</t>
@@ -984,15 +1065,15 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -1001,22 +1082,22 @@
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>41.2</v>
+        <v>35.4</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
         <v>60</v>
       </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>0.3</v>
+      </c>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1030,18 +1111,14 @@
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="n">
-        <v>0.58</v>
-      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>M60</t>
         </is>
       </c>
-      <c r="AF4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
@@ -1050,13 +1127,13 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>18.35</v>
+        <v>18.4</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>VARGUS_D:5</t>
+          <t>VARGUS_D:4</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1080,7 +1157,11 @@
           <t>VHM</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>R262 (DIN 13)</t>
+        </is>
+      </c>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
@@ -1097,11 +1178,22 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R004.0205-15/CN45F</t>
+          <t>L005.0510-15/CN45F</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1123,25 +1215,25 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
         <v>15</v>
       </c>
       <c r="P5" t="n">
-        <v>29.65</v>
+        <v>29.45</v>
       </c>
       <c r="Q5" t="n">
         <v>30</v>
@@ -1149,17 +1241,17 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>0.27</v>
+        <v>0.55</v>
       </c>
       <c r="U5" t="n">
-        <v>0.35</v>
+        <v>0.55</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1185,7 +1277,7 @@
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr"/>
@@ -1193,7 +1285,7 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>VARGUS_D:4</t>
+          <t>VARGUS_D:5</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -1234,105 +1326,122 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>51.59</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>4742.86</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>PMKS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BTH18UN.065916.RETC</t>
+          <t>L004.0205-15/AL41F</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BRICE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VAR_M6</t>
-        </is>
-      </c>
+          <t>DUEMMEL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ULTRAMINI</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PMKNSH</t>
+          <t>PMKNS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>6.3</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>3.5</v>
+      </c>
       <c r="O6" t="n">
-        <v>16</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="P6" t="n">
+        <v>29.65</v>
+      </c>
       <c r="Q6" t="n">
-        <v>42.2</v>
+        <v>30</v>
       </c>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="n">
-        <v>60</v>
-      </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>P</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2A/2B</t>
-        </is>
-      </c>
-      <c r="AA6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.8100000000000001</v>
-      </c>
+          <t>6H</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>UN60</t>
-        </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>1</v>
-      </c>
+          <t>M60</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>18.5</v>
-      </c>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>VARGUS_D:6</t>
+          <t>VARGUS_D:4</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -1342,12 +1451,12 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>VBX</t>
+          <t>AL41F</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>TiCN</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr"/>
@@ -1369,10 +1478,29 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
+          <t>Ultramini,pdf</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>4807.21</v>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
